--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T12:26:45+00:00</t>
+    <t>2026-09-09T12:40:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T12:40:12+00:00</t>
+    <t>2026-09-09T12:51:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T12:51:05+00:00</t>
+    <t>2026-09-09T12:56:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T12:56:34+00:00</t>
+    <t>2026-09-09T13:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:08:30+00:00</t>
+    <t>2026-09-09T13:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:18:24+00:00</t>
+    <t>2026-09-09T13:33:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:33:26+00:00</t>
+    <t>2026-09-09T13:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T13:48:19+00:00</t>
+    <t>2026-09-11T10:07:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
+++ b/branches/fix/go-publish-bootstrap/StructureDefinition-mii-ex-biobank-temperaturbedingungen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:07:49+00:00</t>
+    <t>2026-09-11T10:33:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
